--- a/content/social/content-calendar.xlsx
+++ b/content/social/content-calendar.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Calendar" sheetId="1" r:id="R33217a28c2a041f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Calendar" sheetId="1" r:id="R9639479bd85248a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,8 +13,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="201" formatCode="m/d/yy"/>
   </x:numFmts>
   <x:fonts count="13">
     <x:font>
@@ -130,7 +131,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="58">
+  <x:cellXfs count="59">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -269,6 +270,7 @@
     <x:xf numFmtId="200" fontId="7" fillId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -904,6 +906,110 @@
         <x:v>Publish date = campaign end date − 3 days.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12" ht="92" customHeight="1">
+      <x:c r="A12" s="58" t="n">
+        <x:v>46312</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>product-carousel-001</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>Carousel</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>product-carousel-evergreen</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>4 PNG slides</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>output/social/product-carousels/november/evergreen</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>A full month of math practice, ready to use.</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>November family-learning scene with monthly packet thumbnails.</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>A full month of math practice, ready to use.
+Visit the link in bio.</x:v>
+      </x:c>
+      <x:c r="J12" t="str">
+        <x:v>A full month of math practice, with reading passages, three levels, and answer keys in one packet.</x:v>
+      </x:c>
+      <x:c r="K12" t="str">
+        <x:v>#teacherspayteachers #mathathome #homeschooling #printables</x:v>
+      </x:c>
+      <x:c r="L12" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="M12" t="str"/>
+      <x:c r="N12" t="str">
+        <x:v>MONTHLY_VARIANT</x:v>
+      </x:c>
+      <x:c r="O12" t="str"/>
+      <x:c r="P12" t="str"/>
+      <x:c r="Q12" s="58" t="n">
+        <x:v>46305</x:v>
+      </x:c>
+      <x:c r="R12" t="str">
+        <x:v>Generated by npm run social:product-carousel -- --month november.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="92" customHeight="1">
+      <x:c r="A13" s="58" t="n">
+        <x:v>46326</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>product-carousel-002</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>Carousel</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>product-carousel-campaign-aligned</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>4 PNG slides</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>output/social/product-carousels/november/campaign-aligned</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>November math practice is ready.</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>November weekend family-learning scene with an availability badge.</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>November math practice is ready.
+Get the full packet before the month begins.</x:v>
+      </x:c>
+      <x:c r="J13" t="str">
+        <x:v>November math practice is ready. Find the full packet through the link in bio.</x:v>
+      </x:c>
+      <x:c r="K13" t="str">
+        <x:v>#teacherspayteachers #mathathome #homeschooling #printables</x:v>
+      </x:c>
+      <x:c r="L13" t="str">
+        <x:v>Planned</x:v>
+      </x:c>
+      <x:c r="M13" t="str">
+        <x:v>November release</x:v>
+      </x:c>
+      <x:c r="N13" t="str">
+        <x:v>MONTHLY_VARIANT</x:v>
+      </x:c>
+      <x:c r="O13" t="str"/>
+      <x:c r="P13" t="str"/>
+      <x:c r="Q13" s="58" t="n">
+        <x:v>46319</x:v>
+      </x:c>
+      <x:c r="R13" t="str">
+        <x:v>Campaign-aligned copy must use supplied campaign facts; do not add free or sale claims without dates and offer details.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>

--- a/content/social/content-calendar.xlsx
+++ b/content/social/content-calendar.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Calendar" sheetId="1" r:id="R9639479bd85248a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Calendar" sheetId="1" r:id="R5418a868524a44cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -936,10 +936,10 @@
 Visit the link in bio.</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>A full month of math practice, with reading passages, three levels, and answer keys in one packet.</x:v>
+        <x:v>Some months, the hardest part is keeping practice consistent. This November packet brings reading passages, three levels of math practice, and answer keys into one ready-to-use resource. Save this post, preview the pages, and find the full packet through the link in bio.</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>#teacherspayteachers #mathathome #homeschooling #printables</x:v>
+        <x:v>#novembermath #mathpractice #homeschoolmath #mathathome #teacherspayteachers #printableworksheets #elementarymath #homeschoolresources #mathresources #learningathome #printablelearning</x:v>
       </x:c>
       <x:c r="L12" t="str">
         <x:v>Planned</x:v>
@@ -987,10 +987,10 @@
 Get the full packet before the month begins.</x:v>
       </x:c>
       <x:c r="J13" t="str">
-        <x:v>November math practice is ready. Find the full packet through the link in bio.</x:v>
+        <x:v>November practice is ready. This packet brings reading passages, three levels of daily math practice, and answer keys into one place, so you can start the month with a plan. Preview the pages, then get the full packet through the link in bio.</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>#teacherspayteachers #mathathome #homeschooling #printables</x:v>
+        <x:v>#novembermath #mathpractice #homeschoolmath #mathathome #teacherspayteachers #printableworksheets #elementarymath #homeschoolresources #mathresources #learningathome #printablelearning</x:v>
       </x:c>
       <x:c r="L13" t="str">
         <x:v>Planned</x:v>
